--- a/data/trans_camb/IP07_C13_R_2023-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP07_C13_R_2023-Edad-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -622,645 +631,639 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8,44</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,77</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,27</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-2,07</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,12</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3,73</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>8.43886296571651</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>5.082425488446363</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.1182726135210241</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>11.76980028335907</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>2.268569160063437</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-2.073762509593998</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>10.12264579243166</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>3.726713387573187</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>-1.056678970587086</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>3,49; 14,14</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,96; 9,92</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,04; 4,33</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5,6; 18,58</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-3,27; 6,54</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-7,04; 3,3</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,16; 14,35</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,73; 7,23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-4,2; 2,64</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>3.485175015986921</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.9573732091424372</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.039454200314985</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>5.597364173539233</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-3.2707679870507</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-7.042964831991798</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>6.160856576300891</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0.727577026546677</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>-4.204342764106035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>211,14%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>127,16%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,96%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>192,01%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>37,01%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-33,83%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>202,05%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>74,39%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-21,09%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>14.13645536895177</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.91707488780448</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.32606102117184</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>18.58366767444245</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>6.541150768856041</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>3.296052521131298</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>14.35123648498173</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>7.23370357108718</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>2.640847771662635</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>45,06; 650,14</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5,21; 477,9</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-79,87; 197,7</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>57,67; 533,54</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-37,56; 179,79</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-84,63; 95,97</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,11; 441,01</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9,17; 205,98</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>-68,93; 79,57</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>2.111393011332652</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1.271616531814777</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.0295916607053395</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1.920119930407832</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.3700933535724527</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3383126841356719</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>2.020528317084934</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.7438697435092516</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>-0.2109181557785677</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>6,84</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6,88</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,48</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,84</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,03</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,33</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5,97</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-2,33</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.450597099350529</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.05206359771734562</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.7987092243445227</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.5766883427695452</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3756102417425066</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.846335523544676</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.9110579450167345</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0.09172959154926741</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>-0.6892659148785305</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2,87; 11,75</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2,39; 11,51</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,27; -1,29</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2,96; 13,3</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,23; 9,89</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-4,58; 3,24</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,26; 10,61</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2,89; 9,59</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-4,44; 0,09</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>6.50136001598672</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>4.77902256361644</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1.976963788052292</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>5.335409921230789</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.797893495747395</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.9597191931556959</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>4.41010036418659</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>2.0598167956023</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>0.7956795401871608</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>163,57%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>164,66%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-83,19%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>160,59%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>102,96%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-13,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>161,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>132,02%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>-51,47%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>6.838577109981972</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>6.884144043845711</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.478094639104507</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>7.843438606775665</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>5.028541484692984</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.6689771571827423</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>7.328506480078534</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>5.973821921747551</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>-2.329193552912309</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>34,71; 469,33</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>32,37; 425,1</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; -14,86</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>38,37; 408,99</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,48; 303,9</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-71,54; 113,97</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>71,13; 333,91</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>51,69; 301,3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>-80,18; 5,66</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2.86603772106091</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2.392434106864465</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.269116788944816</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>2.961244590274455</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.227968174788109</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-4.576971885596097</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>4.255569781962431</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>2.885090443927992</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>-4.436411156384328</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>7,58</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5,94</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,24</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,85</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,76</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-1,21</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,7</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4,87</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>-1,88</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>11.75271521632489</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.51470362239707</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-1.289647155179151</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>13.30389924090651</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>9.886180163577666</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>3.240021128782934</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>10.60802864661447</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>9.588206031302958</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0.08604262232562979</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>4,44; 11,2</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2,58; 9,44</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-4,51; 0,15</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5,8; 13,84</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,59; 7,06</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-4,22; 2,04</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,11; 11,18</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2,68; 7,24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-4,01; 0,01</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>1.635702201089437</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1.646601242340141</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.8319167811205116</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1.605905164826945</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1.029568936109094</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1369697559617477</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1.619584754765895</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>1.320202272925459</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>-0.5147469514355075</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>184,66%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>144,66%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-54,57%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>183,6%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>70,03%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-22,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>184,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>103,33%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>-39,84%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0.3471474010109698</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.3237359195035862</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.3836564763989475</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.004770545438639187</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7154154303371564</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0.711275075054995</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0.5168903616026455</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>-0.801813063032234</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>77,78; 391,32</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>47,93; 331,01</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-82,59; 12,98</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>74,14; 337,35</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>4,81; 178,07</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-65,8; 51,66</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>102,56; 295,18</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>42,07; 190,47</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>-68,75; 0,33</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>4.693329595556603</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>4.251045995285817</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-0.1486010844300595</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>4.089915444806898</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>3.038953641147637</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.139713081011509</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>3.339115398254174</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>3.012991270631694</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>0.0566090821152865</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>7.58481653668692</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>5.941876224969633</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.241234838126382</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>9.84815600819452</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>3.756305184014982</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-1.206495905554481</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>8.704648224747693</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>4.871959330670869</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>-1.878515941038116</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>4.443460328769646</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2.581443874452456</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4.505790256066671</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>5.797769405341801</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.5934018937433834</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-4.220015920737455</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>6.107996610450418</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>2.679749326019023</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>-4.010959844125388</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>11.19821278370232</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>9.439315695614884</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.1473908546966609</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>13.8431994731233</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>7.059045562736883</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2.043630216453904</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>11.18450887805934</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>7.24108371785615</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.006530518347550455</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>1.846609177349319</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1.446616818565187</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.5456539127427578</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1.83598864624867</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.7002868013014837</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.2249266545432838</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>1.846095116398137</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>1.033252590503452</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>-0.3983985355050964</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0.7778070019108374</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.4793343262903064</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.825907844313708</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0.74140843450714</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.04813796631664357</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.6579991476553452</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>1.025580216505501</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0.420675338243757</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>-0.6875081843764477</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>3.913167794233436</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>3.310069823647314</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.1298048250564499</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>3.373504165458856</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1.780662205919951</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.5165508637462214</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>2.951791828265611</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>1.904715903380886</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>0.003294117336583693</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1268,12 +1271,12 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A12:A15"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
